--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6086,8 +6086,12 @@
           <t>COLOMBIA</t>
         </is>
       </c>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
+      <c r="D76" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="F76" s="25" t="inlineStr">
         <is>
           <t>2K</t>
@@ -6405,8 +6409,12 @@
           <t>PANAMA</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
+      <c r="D83" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F83" s="25" t="inlineStr">
         <is>
           <t>2L</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1471,8 +1471,12 @@
           <t>SOUTH AFRICA</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
+      <c r="D7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
           <t>3A</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2062,8 +2062,12 @@
           <t>BOSNIA H.</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
+      <c r="D14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F14" s="26" t="inlineStr">
         <is>
           <t>3B</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2160,8 +2160,12 @@
           <t>QATAR</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
+      <c r="D15" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
           <t>4B</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1573,8 +1573,12 @@
           <t>SOUTH KOREA</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" s="18" t="inlineStr">
         <is>
           <t>4A</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3146,8 +3146,12 @@
           <t>AUSTRALIA</t>
         </is>
       </c>
-      <c r="D28" s="40" t="n"/>
-      <c r="E28" s="41" t="n"/>
+      <c r="D28" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="F28" s="26" t="inlineStr">
         <is>
           <t>3D</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2618,8 +2618,12 @@
           <t>MOROCCO</t>
         </is>
       </c>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
+      <c r="D21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F21" s="26" t="inlineStr">
         <is>
           <t>3C</t>
@@ -2700,8 +2704,12 @@
           <t>HAITI</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
+      <c r="D22" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
           <t>4C</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3245,8 +3245,12 @@
           <t>PARAGUAY</t>
         </is>
       </c>
-      <c r="D29" s="40" t="n"/>
-      <c r="E29" s="41" t="n"/>
+      <c r="D29" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
           <t>4D</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4193,8 +4193,12 @@
           <t>SWEDEN</t>
         </is>
       </c>
-      <c r="D42" s="40" t="n"/>
-      <c r="E42" s="41" t="n"/>
+      <c r="D42" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="F42" s="26" t="inlineStr">
         <is>
           <t>3F</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3656,8 +3656,12 @@
           <t>IVORY COAST</t>
         </is>
       </c>
-      <c r="D35" s="40" t="n"/>
-      <c r="E35" s="41" t="n"/>
+      <c r="D35" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="F35" s="26" t="inlineStr">
         <is>
           <t>3E</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3757,8 +3757,12 @@
           <t>CURAÇAO</t>
         </is>
       </c>
-      <c r="D36" s="40" t="n"/>
-      <c r="E36" s="41" t="n"/>
+      <c r="D36" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
           <t>4E</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4291,8 +4291,12 @@
           <t>JAPAN</t>
         </is>
       </c>
-      <c r="D43" s="40" t="n"/>
-      <c r="E43" s="41" t="n"/>
+      <c r="D43" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>4</v>
+      </c>
       <c r="F43" s="27" t="inlineStr">
         <is>
           <t>4F</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5063,8 +5063,12 @@
           <t>SAUDI ARABIA</t>
         </is>
       </c>
-      <c r="D56" s="40" t="n"/>
-      <c r="E56" s="41" t="n"/>
+      <c r="D56" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="F56" s="26" t="inlineStr">
         <is>
           <t>3H</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4679,8 +4679,12 @@
           <t>IRAN</t>
         </is>
       </c>
-      <c r="D49" s="40" t="n"/>
-      <c r="E49" s="41" t="n"/>
+      <c r="D49" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
           <t>3G</t>
@@ -5064,7 +5068,7 @@
         </is>
       </c>
       <c r="D56" s="40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E56" s="41" t="n">
         <v>0</v>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5142,8 +5142,12 @@
           <t>CAPO VERDE</t>
         </is>
       </c>
-      <c r="D57" s="40" t="n"/>
-      <c r="E57" s="41" t="n"/>
+      <c r="D57" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="F57" s="27" t="inlineStr">
         <is>
           <t>4H</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4758,8 +4758,12 @@
           <t>EGYPT</t>
         </is>
       </c>
-      <c r="D50" s="40" t="n"/>
-      <c r="E50" s="41" t="n"/>
+      <c r="D50" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="F50" s="27" t="inlineStr">
         <is>
           <t>4G</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5882,8 +5882,12 @@
           <t>AUSTRIA</t>
         </is>
       </c>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
+      <c r="D70" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F70" s="26" t="inlineStr">
         <is>
           <t>3J</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5503,8 +5503,12 @@
           <t>IRAQ</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
+      <c r="D63" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F63" s="26" t="inlineStr">
         <is>
           <t>3I</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5591,8 +5591,12 @@
           <t>SENEGAL</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
+      <c r="D64" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="F64" s="27" t="inlineStr">
         <is>
           <t>4I</t>
@@ -5950,8 +5954,12 @@
           <t>ALGERIA</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n"/>
-      <c r="E71" s="8" t="n"/>
+      <c r="D71" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="F71" s="27" t="inlineStr">
         <is>
           <t>4J</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6230,8 +6230,12 @@
           <t>UZBEKISTAN</t>
         </is>
       </c>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
+      <c r="D77" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F77" s="26" t="inlineStr">
         <is>
           <t>3K</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6548,8 +6548,12 @@
           <t>GHANA</t>
         </is>
       </c>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
+      <c r="D84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F84" s="26" t="inlineStr">
         <is>
           <t>3L</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6603,8 +6603,12 @@
           <t>CROATIA</t>
         </is>
       </c>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
+      <c r="D85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F85" s="27" t="inlineStr">
         <is>
           <t>4L</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6294,8 +6294,12 @@
           <t>DR CONGO</t>
         </is>
       </c>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
+      <c r="D78" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F78" s="27" t="inlineStr">
         <is>
           <t>4K</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2266,8 +2266,12 @@
           <t>CANADA</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="D16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="H16" s="28" t="n"/>
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
@@ -2328,8 +2332,12 @@
           <t>QATAR</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
+      <c r="D17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F17" s="23" t="n"/>
       <c r="G17" s="23" t="n"/>
       <c r="H17" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1672,8 +1672,12 @@
           <t>MEXICO</t>
         </is>
       </c>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="F9" s="18" t="n"/>
       <c r="G9" s="20" t="n"/>
       <c r="H9" s="21" t="n"/>
@@ -1740,8 +1744,12 @@
           <t>SOUTH KOREA</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="23" t="n"/>
       <c r="H10" s="24" t="n"/>
@@ -2804,8 +2812,12 @@
           <t>BRAZIL</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
+      <c r="D23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="H23" s="28" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
@@ -2863,8 +2875,12 @@
           <t>HAITI</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="D24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="F24" s="23" t="n"/>
       <c r="G24" s="23" t="n"/>
       <c r="H24" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3878,8 +3878,12 @@
           <t>IVORY COAST</t>
         </is>
       </c>
-      <c r="D37" s="40" t="n"/>
-      <c r="E37" s="41" t="n"/>
+      <c r="D37" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="H37" s="28" t="n"/>
       <c r="J37" s="11" t="inlineStr">
         <is>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3943,8 +3943,12 @@
           <t>GERMANY</t>
         </is>
       </c>
-      <c r="D38" s="40" t="n"/>
-      <c r="E38" s="41" t="n"/>
+      <c r="D38" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="F38" s="23" t="n"/>
       <c r="G38" s="23" t="n"/>
       <c r="H38" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4428,8 +4428,12 @@
           <t>SWEDEN</t>
         </is>
       </c>
-      <c r="D44" s="40" t="n"/>
-      <c r="E44" s="41" t="n"/>
+      <c r="D44" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H44" s="28" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -4497,8 +4501,12 @@
           <t>NETHERLANDS</t>
         </is>
       </c>
-      <c r="D45" s="40" t="n"/>
-      <c r="E45" s="41" t="n"/>
+      <c r="D45" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="F45" s="23" t="n"/>
       <c r="G45" s="23" t="n"/>
       <c r="H45" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3364,8 +3364,12 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="D30" s="40" t="n"/>
-      <c r="E30" s="41" t="n"/>
+      <c r="D30" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="41" t="n">
+        <v>2</v>
+      </c>
       <c r="H30" s="28" t="n"/>
       <c r="J30" s="14">
         <f>AU25</f>
@@ -3418,8 +3422,12 @@
           <t>AUSTRALIA</t>
         </is>
       </c>
-      <c r="D31" s="40" t="n"/>
-      <c r="E31" s="41" t="n"/>
+      <c r="D31" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="F31" s="23" t="n"/>
       <c r="G31" s="23" t="n"/>
       <c r="H31" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5715,8 +5715,12 @@
           <t>FRANCE</t>
         </is>
       </c>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
+      <c r="D65" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>4</v>
+      </c>
       <c r="H65" s="28" t="n"/>
       <c r="J65" s="11" t="inlineStr">
         <is>
@@ -5760,8 +5764,12 @@
           <t>IRAQ</t>
         </is>
       </c>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
+      <c r="D66" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F66" s="23" t="n"/>
       <c r="G66" s="23" t="n"/>
       <c r="H66" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5273,8 +5273,12 @@
           <t>SAUDI ARABIA</t>
         </is>
       </c>
-      <c r="D58" s="40" t="n"/>
-      <c r="E58" s="41" t="n"/>
+      <c r="D58" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="41" t="n">
+        <v>0</v>
+      </c>
       <c r="H58" s="28" t="n"/>
       <c r="J58" s="14" t="inlineStr">
         <is>
@@ -5312,8 +5316,12 @@
           <t>SPAIN</t>
         </is>
       </c>
-      <c r="D59" s="40" t="n"/>
-      <c r="E59" s="41" t="n"/>
+      <c r="D59" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="F59" s="23" t="n"/>
       <c r="G59" s="23" t="n"/>
       <c r="H59" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4871,8 +4871,12 @@
           <t>IRAN</t>
         </is>
       </c>
-      <c r="D51" s="40" t="n"/>
-      <c r="E51" s="41" t="n"/>
+      <c r="D51" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="H51" s="28" t="n"/>
       <c r="Y51" s="11" t="inlineStr">
         <is>
@@ -4905,8 +4909,12 @@
           <t>BELGIUM</t>
         </is>
       </c>
-      <c r="D52" s="40" t="n"/>
-      <c r="E52" s="41" t="n"/>
+      <c r="D52" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>5</v>
+      </c>
       <c r="F52" s="23" t="n"/>
       <c r="G52" s="23" t="n"/>
       <c r="H52" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6734,8 +6734,12 @@
           <t>ENGLAND</t>
         </is>
       </c>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
+      <c r="D86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>2</v>
+      </c>
       <c r="H86" s="28" t="n"/>
       <c r="AW86" s="35" t="n"/>
       <c r="AX86" s="3" t="n"/>
@@ -6753,8 +6757,12 @@
           <t>GHANA</t>
         </is>
       </c>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
+      <c r="D87" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F87" s="23" t="n"/>
       <c r="G87" s="23" t="n"/>
       <c r="H87" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6430,8 +6430,12 @@
           <t>PORTUGAL</t>
         </is>
       </c>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="8" t="n"/>
+      <c r="D79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="H79" s="28" t="n"/>
       <c r="N79" s="3" t="n"/>
       <c r="O79" s="3" t="n"/>
@@ -6458,8 +6462,12 @@
           <t>UZBEKISTAN</t>
         </is>
       </c>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
+      <c r="D80" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="F80" s="23" t="n"/>
       <c r="G80" s="23" t="n"/>
       <c r="H80" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -6090,8 +6090,12 @@
           <t>AUSTRIA</t>
         </is>
       </c>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
+      <c r="D72" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="H72" s="28" t="n"/>
       <c r="N72" s="3" t="n"/>
       <c r="O72" s="3" t="n"/>
@@ -6118,8 +6122,12 @@
           <t>ARGENTINA</t>
         </is>
       </c>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
+      <c r="D73" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>3</v>
+      </c>
       <c r="F73" s="23" t="n"/>
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="24" t="n"/>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2000,7 +2000,9 @@
         <f>_xlfn.XLOOKUP(J13,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L13" s="44" t="n"/>
+      <c r="L13" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" s="55" t="inlineStr">
         <is>
           <t>T3</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3904,7 +3904,9 @@
         <f>_xlfn.XLOOKUP(J37,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L37" s="44" t="n"/>
+      <c r="L37" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M37" s="55" t="inlineStr">
         <is>
           <t>T9</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1297,7 +1297,9 @@
         <f>_xlfn.XLOOKUP(J5,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L5" s="44" t="n"/>
+      <c r="L5" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="M5" s="55" t="inlineStr">
         <is>
           <t>T1</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2362,7 +2362,9 @@
         <f>_xlfn.XLOOKUP(J17,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L17" s="44" t="n"/>
+      <c r="L17" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="M17" s="55" t="inlineStr">
         <is>
           <t>T4</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4187,7 +4187,9 @@
         <f>_xlfn.XLOOKUP(J41,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L41" s="44" t="n"/>
+      <c r="L41" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="M41" s="55" t="inlineStr">
         <is>
           <t>T10</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1692,7 +1692,9 @@
         <f>_xlfn.XLOOKUP(J9,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L9" s="44" t="n"/>
+      <c r="L9" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M9" s="55" t="inlineStr">
         <is>
           <t>T2</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4539,7 +4539,9 @@
         <f>_xlfn.XLOOKUP(J45,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L45" s="44" t="n"/>
+      <c r="L45" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M45" s="55" t="inlineStr">
         <is>
           <t>T11</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4769,7 +4769,9 @@
         <f>_xlfn.XLOOKUP(J49,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L49" s="44" t="n"/>
+      <c r="L49" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M49" s="55" t="inlineStr">
         <is>
           <t>T12</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3557,7 +3557,9 @@
         <f>_xlfn.XLOOKUP(J33,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L33" s="44" t="n"/>
+      <c r="L33" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M33" s="55" t="inlineStr">
         <is>
           <t>T8</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3305,7 +3305,9 @@
         <f>_xlfn.XLOOKUP(J29,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L29" s="44" t="n"/>
+      <c r="L29" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M29" s="55" t="inlineStr">
         <is>
           <t>T7</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2953,7 +2953,9 @@
         <f>_xlfn.XLOOKUP(J25,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L25" s="44" t="n"/>
+      <c r="L25" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M25" s="55" t="inlineStr">
         <is>
           <t>T6</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2670,7 +2670,9 @@
         <f>_xlfn.XLOOKUP(J21,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L21" s="44" t="n"/>
+      <c r="L21" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M21" s="55" t="inlineStr">
         <is>
           <t>T5</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5466,7 +5466,9 @@
         <f>_xlfn.XLOOKUP(J61,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L61" s="44" t="n"/>
+      <c r="L61" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M61" s="55" t="inlineStr">
         <is>
           <t>T15</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5254,7 +5254,9 @@
         <f>_xlfn.XLOOKUP(J57,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L57" s="44" t="n"/>
+      <c r="L57" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="M57" s="55" t="inlineStr">
         <is>
           <t>T14</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4979,7 +4979,9 @@
         <f>_xlfn.XLOOKUP(J53,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L53" s="44" t="n"/>
+      <c r="L53" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M53" s="55" t="inlineStr">
         <is>
           <t>T13</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5777,7 +5777,9 @@
         <f>_xlfn.XLOOKUP(J65,$F$5:$F$85,$G$5:$G$85, "")</f>
         <v/>
       </c>
-      <c r="L65" s="44" t="n"/>
+      <c r="L65" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="M65" s="55" t="inlineStr">
         <is>
           <t>T16</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2211,7 +2211,9 @@
         <f>IF(L13="","",IF(L13=1, K13, K14))</f>
         <v/>
       </c>
-      <c r="Q15" s="44" t="n"/>
+      <c r="Q15" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R15" s="55" t="inlineStr">
         <is>
           <t>Q2</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1506,7 +1506,9 @@
         <f>IF(L5="","",IF(L5=1, K5, K6))</f>
         <v/>
       </c>
-      <c r="Q7" s="44" t="n"/>
+      <c r="Q7" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R7" s="55" t="inlineStr">
         <is>
           <t>Q1</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4050,7 +4050,9 @@
         <f>IF(L37="","",IF(L37=1, K37, K38))</f>
         <v/>
       </c>
-      <c r="Q39" s="44" t="n"/>
+      <c r="Q39" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R39" s="55" t="inlineStr">
         <is>
           <t>Q5</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4647,7 +4647,9 @@
         <f>IF(L45="","",IF(L45=1, K45, K46))</f>
         <v/>
       </c>
-      <c r="Q47" s="44" t="n"/>
+      <c r="Q47" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R47" s="55" t="inlineStr">
         <is>
           <t>Q6</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2847,7 +2847,9 @@
         <f>IF(L21="","",IF(L21=1, K21, K22))</f>
         <v/>
       </c>
-      <c r="Q23" s="44" t="n"/>
+      <c r="Q23" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R23" s="55" t="inlineStr">
         <is>
           <t>Q3</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3465,7 +3465,9 @@
         <f>IF(L29="","",IF(L29=1, K29, K30))</f>
         <v/>
       </c>
-      <c r="Q31" s="44" t="n"/>
+      <c r="Q31" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="R31" s="55" t="inlineStr">
         <is>
           <t>Q4</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5109,7 +5109,9 @@
         <f>IF(L53="","",IF(L53=1, K53, K54))</f>
         <v/>
       </c>
-      <c r="Q55" s="44" t="n"/>
+      <c r="Q55" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" s="55" t="inlineStr">
         <is>
           <t>Q7</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5639,7 +5639,9 @@
         <f>IF(L61="","",IF(L61=1, K61, K62))</f>
         <v/>
       </c>
-      <c r="Q63" s="44" t="n"/>
+      <c r="Q63" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="R63" s="55" t="inlineStr">
         <is>
           <t>Q8</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -1836,7 +1836,9 @@
         <f>IF(Q7="","",IF(Q7=1, P7, P8))</f>
         <v/>
       </c>
-      <c r="V11" s="44" t="n"/>
+      <c r="V11" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="W11" s="55" t="inlineStr">
         <is>
           <t>S1</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3141,7 +3141,9 @@
         <f>IF(Q23="","",IF(Q23=1, P23, P24))</f>
         <v/>
       </c>
-      <c r="V27" s="44" t="n"/>
+      <c r="V27" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="W27" s="55" t="inlineStr">
         <is>
           <t>S2</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4403,7 +4403,9 @@
         <f>IF(Q39="","",IF(Q39=1, P39, P40))</f>
         <v/>
       </c>
-      <c r="V43" s="44" t="n"/>
+      <c r="V43" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="W43" s="55" t="inlineStr">
         <is>
           <t>S3</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -5390,7 +5390,9 @@
         <f>IF(Q55="","",IF(Q55=1, P55, P56))</f>
         <v/>
       </c>
-      <c r="V59" s="44" t="n"/>
+      <c r="V59" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="W59" s="55" t="inlineStr">
         <is>
           <t>S4</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -2514,7 +2514,9 @@
         <f>IF(V11="","",IF(V11=1, U11, U12))</f>
         <v/>
       </c>
-      <c r="AA19" s="44" t="n"/>
+      <c r="AA19" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="AB19" s="55" t="inlineStr">
         <is>
           <t>F1</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4931,7 +4931,9 @@
         <f>IF(V43="","",IF(V43=1, U43, U44))</f>
         <v/>
       </c>
-      <c r="AA51" s="44" t="n"/>
+      <c r="AA51" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="AB51" s="55" t="inlineStr">
         <is>
           <t>F2</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4427,7 +4427,9 @@
         <f>IF(AA19="","",IF(AA19=1, Z20, Z19))</f>
         <v/>
       </c>
-      <c r="AF43" s="44" t="n"/>
+      <c r="AF43" s="44" t="n">
+        <v>2</v>
+      </c>
       <c r="AG43" s="55" t="inlineStr">
         <is>
           <t>TW</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -3765,7 +3765,9 @@
         <f>IF(AA19="","",IF(AA19=1, Z19, Z20))</f>
         <v/>
       </c>
-      <c r="AF35" s="44" t="n"/>
+      <c r="AF35" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="AG35" s="55" t="inlineStr">
         <is>
           <t>CW</t>

--- a/data/FIFAWC2026_Model.xlsx
+++ b/data/FIFAWC2026_Model.xlsx
@@ -4524,14 +4524,12 @@
       <c r="AG44" s="56" t="n"/>
       <c r="AI44" s="42" t="inlineStr">
         <is>
-          <t>PLAYER NAME</t>
+          <t>Kylian Mbappe</t>
         </is>
       </c>
       <c r="AJ44" s="43" t="n"/>
-      <c r="AK44" s="42" t="inlineStr">
-        <is>
-          <t># GOALS</t>
-        </is>
+      <c r="AK44" s="42" t="n">
+        <v>10</v>
       </c>
       <c r="AL44" s="43" t="n"/>
       <c r="AW44" s="35" t="n"/>
